--- a/room.xlsx
+++ b/room.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$680</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$678</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4761" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4747" uniqueCount="806">
   <si>
     <t>Id</t>
   </si>
@@ -2460,14 +2460,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2923,28 +2916,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2953,118 +2949,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3416,12 +3409,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H680"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="5" max="5" width="19.875" customWidth="1"/>
-    <col min="6" max="6" width="27.5" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="1" max="1" width="17.7345132743363" customWidth="1"/>
+    <col min="5" max="5" width="26.8849557522124" customWidth="1"/>
+    <col min="6" max="6" width="27.5044247787611" customWidth="1"/>
+    <col min="7" max="7" width="25.8230088495575" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -20482,10 +20476,10 @@
     </row>
     <row r="657" spans="1:8">
       <c r="A657" t="s">
-        <v>549</v>
+        <v>781</v>
       </c>
       <c r="B657">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C657" t="s">
         <v>550</v>
@@ -20500,7 +20494,7 @@
         <v>774</v>
       </c>
       <c r="G657" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H657" t="s">
         <v>536</v>
@@ -20508,10 +20502,10 @@
     </row>
     <row r="658" spans="1:8">
       <c r="A658" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B658">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C658" t="s">
         <v>550</v>
@@ -20534,16 +20528,16 @@
     </row>
     <row r="659" spans="1:8">
       <c r="A659" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B659">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C659" t="s">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="D659" t="s">
-        <v>535</v>
+        <v>43</v>
       </c>
       <c r="E659" t="s">
         <v>774</v>
@@ -20555,15 +20549,15 @@
         <v>28</v>
       </c>
       <c r="H659" t="s">
-        <v>536</v>
+        <v>46</v>
       </c>
     </row>
     <row r="660" spans="1:8">
       <c r="A660" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B660">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C660" t="s">
         <v>219</v>
@@ -20586,13 +20580,13 @@
     </row>
     <row r="661" spans="1:8">
       <c r="A661" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B661">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C661" t="s">
-        <v>219</v>
+        <v>338</v>
       </c>
       <c r="D661" t="s">
         <v>43</v>
@@ -20604,7 +20598,7 @@
         <v>774</v>
       </c>
       <c r="G661" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="H661" t="s">
         <v>46</v>
@@ -20612,10 +20606,10 @@
     </row>
     <row r="662" spans="1:8">
       <c r="A662" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B662">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C662" t="s">
         <v>338</v>
@@ -20638,13 +20632,13 @@
     </row>
     <row r="663" spans="1:8">
       <c r="A663" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B663">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C663" t="s">
-        <v>338</v>
+        <v>378</v>
       </c>
       <c r="D663" t="s">
         <v>43</v>
@@ -20656,7 +20650,7 @@
         <v>774</v>
       </c>
       <c r="G663" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="H663" t="s">
         <v>46</v>
@@ -20664,7 +20658,7 @@
     </row>
     <row r="664" spans="1:8">
       <c r="A664" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B664">
         <v>6</v>
@@ -20690,13 +20684,13 @@
     </row>
     <row r="665" spans="1:8">
       <c r="A665" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B665">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C665" t="s">
-        <v>378</v>
+        <v>253</v>
       </c>
       <c r="D665" t="s">
         <v>43</v>
@@ -20716,16 +20710,16 @@
     </row>
     <row r="666" spans="1:8">
       <c r="A666" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B666">
         <v>18</v>
       </c>
       <c r="C666" t="s">
-        <v>253</v>
+        <v>744</v>
       </c>
       <c r="D666" t="s">
-        <v>43</v>
+        <v>744</v>
       </c>
       <c r="E666" t="s">
         <v>774</v>
@@ -20734,24 +20728,24 @@
         <v>774</v>
       </c>
       <c r="G666" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H666" t="s">
-        <v>46</v>
+        <v>745</v>
       </c>
     </row>
     <row r="667" spans="1:8">
       <c r="A667" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B667">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C667" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D667" t="s">
-        <v>744</v>
+        <v>663</v>
       </c>
       <c r="E667" t="s">
         <v>774</v>
@@ -20760,24 +20754,24 @@
         <v>774</v>
       </c>
       <c r="G667" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="H667" t="s">
-        <v>745</v>
+        <v>664</v>
       </c>
     </row>
     <row r="668" spans="1:8">
       <c r="A668" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B668">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C668" t="s">
-        <v>738</v>
+        <v>224</v>
       </c>
       <c r="D668" t="s">
-        <v>663</v>
+        <v>43</v>
       </c>
       <c r="E668" t="s">
         <v>774</v>
@@ -20786,18 +20780,18 @@
         <v>774</v>
       </c>
       <c r="G668" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="H668" t="s">
-        <v>664</v>
+        <v>46</v>
       </c>
     </row>
     <row r="669" spans="1:8">
       <c r="A669" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B669">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C669" t="s">
         <v>224</v>
@@ -20820,10 +20814,10 @@
     </row>
     <row r="670" spans="1:8">
       <c r="A670" t="s">
-        <v>232</v>
+        <v>794</v>
       </c>
       <c r="B670">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="C670" t="s">
         <v>224</v>
@@ -20846,7 +20840,7 @@
     </row>
     <row r="671" spans="1:8">
       <c r="A671" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B671">
         <v>8</v>
@@ -20872,10 +20866,10 @@
     </row>
     <row r="672" spans="1:8">
       <c r="A672" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B672">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C672" t="s">
         <v>224</v>
@@ -20898,16 +20892,16 @@
     </row>
     <row r="673" spans="1:8">
       <c r="A673" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B673">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C673" t="s">
-        <v>224</v>
+        <v>798</v>
       </c>
       <c r="D673" t="s">
-        <v>43</v>
+        <v>535</v>
       </c>
       <c r="E673" t="s">
         <v>774</v>
@@ -20916,24 +20910,24 @@
         <v>774</v>
       </c>
       <c r="G673" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H673" t="s">
-        <v>46</v>
+        <v>536</v>
       </c>
     </row>
     <row r="674" spans="1:8">
       <c r="A674" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B674">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C674" t="s">
-        <v>224</v>
+        <v>798</v>
       </c>
       <c r="D674" t="s">
-        <v>43</v>
+        <v>535</v>
       </c>
       <c r="E674" t="s">
         <v>774</v>
@@ -20942,18 +20936,18 @@
         <v>774</v>
       </c>
       <c r="G674" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H674" t="s">
-        <v>46</v>
+        <v>536</v>
       </c>
     </row>
     <row r="675" spans="1:8">
       <c r="A675" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="B675">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C675" t="s">
         <v>798</v>
@@ -20976,13 +20970,13 @@
     </row>
     <row r="676" spans="1:8">
       <c r="A676" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B676">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C676" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D676" t="s">
         <v>535</v>
@@ -21002,16 +20996,16 @@
     </row>
     <row r="677" spans="1:8">
       <c r="A677" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B677">
         <v>12</v>
       </c>
       <c r="C677" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="D677" t="s">
-        <v>535</v>
+        <v>390</v>
       </c>
       <c r="E677" t="s">
         <v>774</v>
@@ -21020,24 +21014,24 @@
         <v>774</v>
       </c>
       <c r="G677" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H677" t="s">
-        <v>536</v>
+        <v>391</v>
       </c>
     </row>
     <row r="678" spans="1:8">
       <c r="A678" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B678">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C678" t="s">
-        <v>802</v>
+        <v>406</v>
       </c>
       <c r="D678" t="s">
-        <v>535</v>
+        <v>390</v>
       </c>
       <c r="E678" t="s">
         <v>774</v>
@@ -21046,66 +21040,14 @@
         <v>774</v>
       </c>
       <c r="G678" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H678" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="679" spans="1:8">
-      <c r="A679" t="s">
-        <v>803</v>
-      </c>
-      <c r="B679">
-        <v>12</v>
-      </c>
-      <c r="C679" t="s">
-        <v>804</v>
-      </c>
-      <c r="D679" t="s">
-        <v>390</v>
-      </c>
-      <c r="E679" t="s">
-        <v>774</v>
-      </c>
-      <c r="F679" t="s">
-        <v>774</v>
-      </c>
-      <c r="G679" t="s">
-        <v>32</v>
-      </c>
-      <c r="H679" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="680" spans="1:8">
-      <c r="A680" t="s">
-        <v>805</v>
-      </c>
-      <c r="B680">
-        <v>10</v>
-      </c>
-      <c r="C680" t="s">
-        <v>406</v>
-      </c>
-      <c r="D680" t="s">
-        <v>390</v>
-      </c>
-      <c r="E680" t="s">
-        <v>774</v>
-      </c>
-      <c r="F680" t="s">
-        <v>774</v>
-      </c>
-      <c r="G680" t="s">
-        <v>13</v>
-      </c>
-      <c r="H680" t="s">
-        <v>391</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H680" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H678" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
